--- a/study_case_model/smaller_network/scenario_variables/demand_scenarios152.xlsx
+++ b/study_case_model/smaller_network/scenario_variables/demand_scenarios152.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86176.06844275274</v>
+        <v>2298.02849180674</v>
       </c>
     </row>
     <row r="3">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>47926.03548243223</v>
+        <v>1917.041419297289</v>
       </c>
     </row>
     <row r="6">
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14928.8320178776</v>
+        <v>1194.306561430208</v>
       </c>
     </row>
     <row r="9">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>109268.1717691806</v>
+        <v>2913.817913844815</v>
       </c>
     </row>
     <row r="12">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>46487.69937914996</v>
+        <v>1859.507975165998</v>
       </c>
     </row>
     <row r="15">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11621.98641144057</v>
+        <v>929.7589129152458</v>
       </c>
     </row>
     <row r="18">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>110532.2883489163</v>
+        <v>2947.527689304435</v>
       </c>
     </row>
     <row r="21">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>61511.52093729363</v>
+        <v>2460.460837491745</v>
       </c>
     </row>
     <row r="24">
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>10739.47105274393</v>
+        <v>859.1576842195143</v>
       </c>
     </row>
     <row r="27">
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>87207.6009806842</v>
+        <v>2325.536026151579</v>
       </c>
     </row>
     <row r="30">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>43048.73460781306</v>
+        <v>1721.949384312523</v>
       </c>
     </row>
     <row r="33">
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>10753.51342411154</v>
+        <v>860.281073928923</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>80444.15111023576</v>
+        <v>2145.17736293962</v>
       </c>
     </row>
     <row r="39">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>21300.79633013303</v>
+        <v>852.0318532053212</v>
       </c>
     </row>
     <row r="42">
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6031.558128076127</v>
+        <v>482.5246502460902</v>
       </c>
     </row>
     <row r="45">
